--- a/data/trans_orig/IP22D3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Habitat-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26347</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>40870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49072</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82183</t>
+          <t>82292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2556</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>621</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>621</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5759</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10040</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8272</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10127</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8471</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10748</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9300</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10225</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>19999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -946,82 +946,82 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4048</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8190</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>53,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5511</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>439</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11598</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13991</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14921</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>964</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>767</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -1971,74 +1971,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10370</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6491</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>57,27%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11068</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7988</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11408</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12175</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>69,81%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>10656</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>6786</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11701</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>58,0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -2046,27 +2046,27 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11334</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,107 +2427,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2273</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5123</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>36,27%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9858</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11667</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>79,79%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>51,79%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11332</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>13471</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>80,23%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -2766,82 +2766,82 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13022</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>40483</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>34183</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>44487</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>83,47%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>44630</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>40870</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>46866</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>84,85%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82292</t>
+          <t>73751</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94198</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -3222,82 +3222,82 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -3335,82 +3335,82 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
